--- a/data/gravel/Black Mountain Cycles Mod Zero 2025.xlsx
+++ b/data/gravel/Black Mountain Cycles Mod Zero 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB78933A-3B28-954E-B612-1AFEA89FFECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA2823B5-780D-F942-82A1-27A996661878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5060" yWindow="1280" windowWidth="23740" windowHeight="14520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8420" yWindow="2320" windowWidth="23740" windowHeight="14520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="106">
   <si>
     <t>brand</t>
   </si>
@@ -266,9 +266,6 @@
     <t>Black Mountain Cycles</t>
   </si>
   <si>
-    <t>threaded 73</t>
-  </si>
-  <si>
     <t>yes</t>
   </si>
   <si>
@@ -290,9 +287,6 @@
     <t>https://blackmtncycles.com/mod-zero-tech-info/</t>
   </si>
   <si>
-    <t>https://images.theradavist.com/uploads/2025/01/Black-Mountain-Cycles-Mod-Zero-Gravel-Bike-Review-1.jpg</t>
-  </si>
-  <si>
     <t>44cm</t>
   </si>
   <si>
@@ -354,6 +348,9 @@
   </si>
   <si>
     <t>Wheelbase</t>
+  </si>
+  <si>
+    <t>https://blackmtncycles.com/wpblackmtn/wp-content/uploads/2023/06/DSC09580-1200x800.jpeg</t>
   </si>
 </sst>
 </file>
@@ -712,7 +709,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -736,12 +733,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -757,25 +754,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E8" t="s">
         <v>86</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>87</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>88</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
         <v>89</v>
-      </c>
-      <c r="G8" t="s">
-        <v>90</v>
-      </c>
-      <c r="H8" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -783,7 +780,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C9">
         <v>440</v>
@@ -809,7 +806,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C10">
         <v>71</v>
@@ -835,7 +832,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C11">
         <v>74</v>
@@ -861,7 +858,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C12">
         <v>530</v>
@@ -887,7 +884,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C13">
         <v>438</v>
@@ -913,7 +910,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C14">
         <v>72</v>
@@ -939,7 +936,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C15">
         <v>120</v>
@@ -965,7 +962,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C16">
         <v>410</v>
@@ -991,7 +988,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C17">
         <v>55</v>
@@ -1017,7 +1014,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C18">
         <v>64.099999999999994</v>
@@ -1043,7 +1040,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C19">
         <v>567</v>
@@ -1069,7 +1066,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C20">
         <v>368</v>
@@ -1095,7 +1092,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C21">
         <v>756</v>
@@ -1121,7 +1118,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C22">
         <v>600</v>
@@ -1147,7 +1144,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C23">
         <v>1028</v>
@@ -1207,25 +1204,31 @@
       <c r="G28">
         <v>700</v>
       </c>
+      <c r="H28">
+        <v>700</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>28</v>
       </c>
       <c r="C29">
-        <v>2.2999999999999998</v>
+        <v>40</v>
       </c>
       <c r="D29">
-        <v>2.2999999999999998</v>
+        <v>40</v>
       </c>
       <c r="E29">
-        <v>2.2999999999999998</v>
+        <v>40</v>
       </c>
       <c r="F29">
-        <v>2.2999999999999998</v>
+        <v>40</v>
       </c>
       <c r="G29">
-        <v>2.2999999999999998</v>
+        <v>40</v>
+      </c>
+      <c r="H29">
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
@@ -1233,19 +1236,22 @@
         <v>29</v>
       </c>
       <c r="C30">
-        <v>2.2999999999999998</v>
+        <v>50</v>
       </c>
       <c r="D30">
-        <v>2.2999999999999998</v>
+        <v>50</v>
       </c>
       <c r="E30">
-        <v>2.2999999999999998</v>
+        <v>50</v>
       </c>
       <c r="F30">
-        <v>2.2999999999999998</v>
+        <v>50</v>
       </c>
       <c r="G30">
-        <v>2.2999999999999998</v>
+        <v>50</v>
+      </c>
+      <c r="H30">
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
@@ -1270,7 +1276,11 @@
       </c>
       <c r="G31">
         <f t="shared" si="0"/>
-        <v>185.42000000000002</v>
+        <v>182.88</v>
+      </c>
+      <c r="H31">
+        <f>H33*2.54</f>
+        <v>187.96</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
@@ -1291,14 +1301,18 @@
       </c>
       <c r="F32">
         <f t="shared" si="0"/>
-        <v>187.96</v>
+        <v>185.42000000000002</v>
       </c>
       <c r="G32">
         <f t="shared" si="0"/>
+        <v>190.5</v>
+      </c>
+      <c r="H32">
+        <f>H34*2.54</f>
         <v>198.12</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C33">
         <v>60</v>
       </c>
@@ -1312,10 +1326,13 @@
         <v>70</v>
       </c>
       <c r="G33">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+      <c r="H33">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -1332,13 +1349,16 @@
         <v>71</v>
       </c>
       <c r="F34">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G34">
+        <v>75</v>
+      </c>
+      <c r="H34">
         <v>78</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>70</v>
       </c>
@@ -1346,7 +1366,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>72</v>
       </c>
@@ -1354,15 +1374,15 @@
         <v>73</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>74</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>34</v>
       </c>
@@ -1370,75 +1390,73 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>38</v>
       </c>
       <c r="B41">
-        <v>2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>39</v>
       </c>
       <c r="B42">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>44</v>
       </c>
       <c r="B47">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>45</v>
       </c>
       <c r="B48">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>46</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>77</v>
-      </c>
+      <c r="B49" s="1"/>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
@@ -1450,7 +1468,7 @@
         <v>48</v>
       </c>
       <c r="B51">
-        <v>30.9</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
@@ -1458,7 +1476,7 @@
         <v>49</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
@@ -1466,7 +1484,7 @@
         <v>50</v>
       </c>
       <c r="B53">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -1474,7 +1492,7 @@
         <v>51</v>
       </c>
       <c r="B54">
-        <v>38</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -1482,7 +1500,7 @@
         <v>52</v>
       </c>
       <c r="B55">
-        <v>180</v>
+        <v>160</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -1490,7 +1508,7 @@
         <v>53</v>
       </c>
       <c r="B56">
-        <v>180</v>
+        <v>160</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -1508,13 +1526,16 @@
         <v>56</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>57</v>
       </c>
+      <c r="B60" s="1" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
@@ -1555,7 +1576,7 @@
         <v>63</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
@@ -1563,7 +1584,7 @@
         <v>64</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
@@ -1571,7 +1592,7 @@
         <v>65</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
@@ -1579,13 +1600,16 @@
         <v>66</v>
       </c>
       <c r="B69">
-        <v>1195</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>67</v>
       </c>
+      <c r="B70">
+        <v>3975</v>
+      </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
@@ -1597,15 +1621,15 @@
         <v>69</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>80</v>
+      </c>
+      <c r="B73" t="s">
         <v>81</v>
-      </c>
-      <c r="B73" t="s">
-        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Black Mountain Cycles Mod Zero 2025.xlsx
+++ b/data/gravel/Black Mountain Cycles Mod Zero 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA2823B5-780D-F942-82A1-27A996661878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEECF357-C0E3-5F43-86B1-C20D64A3EF7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8420" yWindow="2320" windowWidth="23740" windowHeight="14520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5060" yWindow="2320" windowWidth="23740" windowHeight="14520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -351,6 +351,24 @@
   </si>
   <si>
     <t>https://blackmtncycles.com/wpblackmtn/wp-content/uploads/2023/06/DSC09580-1200x800.jpeg</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -690,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1454,126 +1472,114 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>46</v>
-      </c>
-      <c r="B49" s="1"/>
+        <v>106</v>
+      </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>48</v>
-      </c>
-      <c r="B51">
-        <v>27.2</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>49</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>50</v>
-      </c>
-      <c r="B53">
-        <v>42</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>51</v>
-      </c>
-      <c r="B54">
-        <v>50</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>52</v>
-      </c>
-      <c r="B55">
-        <v>160</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="B55" s="1"/>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>53</v>
-      </c>
-      <c r="B56">
-        <v>160</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>54</v>
+        <v>48</v>
+      </c>
+      <c r="B57">
+        <v>27.2</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>56</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>78</v>
+        <v>50</v>
+      </c>
+      <c r="B59">
+        <v>42</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>57</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>77</v>
+        <v>51</v>
+      </c>
+      <c r="B60">
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>58</v>
+        <v>52</v>
+      </c>
+      <c r="B61">
+        <v>160</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>60</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>62</v>
-      </c>
-      <c r="B65">
-        <v>3</v>
+        <v>56</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>77</v>
@@ -1581,54 +1587,96 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>64</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>65</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>77</v>
+        <v>59</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B69">
-        <v>1145</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>67</v>
-      </c>
-      <c r="B70">
-        <v>3975</v>
+        <v>61</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>68</v>
+        <v>62</v>
+      </c>
+      <c r="B71">
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>64</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>65</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>66</v>
+      </c>
+      <c r="B75">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>67</v>
+      </c>
+      <c r="B76">
+        <v>3975</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>69</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>80</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>81</v>
       </c>
     </row>
